--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008415679646344133</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9797606</v>
+        <v>4804524</v>
       </c>
       <c r="L2" t="n">
-        <v>6211972</v>
+        <v>2971084</v>
       </c>
       <c r="M2" t="n">
-        <v>1642740</v>
+        <v>768782</v>
       </c>
       <c r="N2" t="n">
-        <v>100959</v>
+        <v>42420</v>
       </c>
       <c r="O2" t="n">
-        <v>958692</v>
+        <v>456954</v>
       </c>
       <c r="P2" t="n">
-        <v>353585</v>
+        <v>171836</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999998152256012</v>
+        <v>0.9999973177909851</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9755073189735413</v>
+        <v>0.953692615032196</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9272610545158386</v>
+        <v>0.8909243941307068</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9312231540679932</v>
+        <v>0.8720778822898865</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7748017907142639</v>
+        <v>0.6742215752601624</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9310039281845093</v>
+        <v>0.886717677116394</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9654461741447449</v>
+        <v>0.933085024356842</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -795,16 +795,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9797606</v>
+        <v>4804524</v>
       </c>
       <c r="E3" t="n">
-        <v>273256</v>
+        <v>227604</v>
       </c>
       <c r="F3" t="n">
-        <v>1715</v>
+        <v>1557</v>
       </c>
       <c r="G3" t="n">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="H3" t="n">
         <v>100</v>
@@ -813,109 +813,109 @@
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>20033221</v>
+        <v>10016605</v>
       </c>
       <c r="K3" t="n">
-        <v>22340169</v>
+        <v>11062174</v>
       </c>
       <c r="L3" t="n">
-        <v>25657232</v>
+        <v>12706498</v>
       </c>
       <c r="M3" t="n">
-        <v>30674707</v>
+        <v>15285018</v>
       </c>
       <c r="N3" t="n">
-        <v>32451787</v>
+        <v>16220039</v>
       </c>
       <c r="O3" t="n">
-        <v>31570394</v>
+        <v>15762249</v>
       </c>
       <c r="P3" t="n">
-        <v>32260000</v>
+        <v>16123995</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9726567268371582</v>
+        <v>0.9543886184692383</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9535359144210815</v>
+        <v>0.9115563631057739</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8816927671432495</v>
+        <v>0.825039803981781</v>
       </c>
       <c r="U3" t="n">
-        <v>0.566965639591217</v>
+        <v>0.4762867093086243</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9419645667076111</v>
+        <v>0.8977961540222168</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9147318005561829</v>
+        <v>0.8890429735183716</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>230259</v>
+        <v>217908</v>
       </c>
       <c r="E4" t="n">
-        <v>6211972</v>
+        <v>2971084</v>
       </c>
       <c r="F4" t="n">
-        <v>70309</v>
+        <v>68238</v>
       </c>
       <c r="G4" t="n">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
         <v>1081</v>
@@ -947,109 +947,109 @@
         <v>42</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>245995</v>
+        <v>233288</v>
       </c>
       <c r="L4" t="n">
-        <v>487298</v>
+        <v>363749</v>
       </c>
       <c r="M4" t="n">
-        <v>121327</v>
+        <v>112770</v>
       </c>
       <c r="N4" t="n">
-        <v>29344</v>
+        <v>20497</v>
       </c>
       <c r="O4" t="n">
-        <v>71048</v>
+        <v>58378</v>
       </c>
       <c r="P4" t="n">
-        <v>12655</v>
+        <v>12323</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999991059303284</v>
+        <v>0.9999986290931702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.974079966545105</v>
+        <v>0.9540404677391052</v>
       </c>
       <c r="S4" t="n">
-        <v>0.940214991569519</v>
+        <v>0.9011223316192627</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9057813882827759</v>
+        <v>0.8479070067405701</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6547870635986328</v>
+        <v>0.5582276582717896</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9364522099494934</v>
+        <v>0.89222252368927</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9394050240516663</v>
+        <v>0.910531759262085</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>9277</v>
+        <v>8984</v>
       </c>
       <c r="E5" t="n">
-        <v>171121</v>
+        <v>116083</v>
       </c>
       <c r="F5" t="n">
-        <v>1642740</v>
+        <v>768782</v>
       </c>
       <c r="G5" t="n">
-        <v>10817</v>
+        <v>8770</v>
       </c>
       <c r="H5" t="n">
-        <v>28583</v>
+        <v>28565</v>
       </c>
       <c r="I5" t="n">
         <v>628</v>
@@ -1080,106 +1080,106 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>275430</v>
+        <v>229614</v>
       </c>
       <c r="L5" t="n">
-        <v>302698</v>
+        <v>288269</v>
       </c>
       <c r="M5" t="n">
-        <v>220426</v>
+        <v>163030</v>
       </c>
       <c r="N5" t="n">
-        <v>77110</v>
+        <v>46644</v>
       </c>
       <c r="O5" t="n">
-        <v>59066</v>
+        <v>52019</v>
       </c>
       <c r="P5" t="n">
-        <v>32960</v>
+        <v>21446</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9999989867210388</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9840343594551086</v>
+        <v>0.9716525673866272</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9758109450340271</v>
+        <v>0.9600713849067688</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9895358085632324</v>
+        <v>0.9831104278564453</v>
       </c>
       <c r="U5" t="n">
-        <v>0.996740460395813</v>
+        <v>0.9958884119987488</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9960160255432129</v>
+        <v>0.9932394623756409</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9986032843589783</v>
+        <v>0.9979320168495178</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6409</v>
+        <v>6346</v>
       </c>
       <c r="E6" t="n">
-        <v>41889</v>
+        <v>19033</v>
       </c>
       <c r="F6" t="n">
-        <v>19191</v>
+        <v>12984</v>
       </c>
       <c r="G6" t="n">
-        <v>100959</v>
+        <v>42420</v>
       </c>
       <c r="H6" t="n">
-        <v>9312</v>
+        <v>7976</v>
       </c>
       <c r="I6" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1266,19 +1266,19 @@
         <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F7" t="n">
-        <v>29759</v>
+        <v>29654</v>
       </c>
       <c r="G7" t="n">
-        <v>16682</v>
+        <v>10069</v>
       </c>
       <c r="H7" t="n">
-        <v>958692</v>
+        <v>456954</v>
       </c>
       <c r="I7" t="n">
-        <v>11674</v>
+        <v>11346</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G8" t="n">
-        <v>486</v>
+        <v>312</v>
       </c>
       <c r="H8" t="n">
-        <v>31972</v>
+        <v>20656</v>
       </c>
       <c r="I8" t="n">
-        <v>353585</v>
+        <v>171836</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
